--- a/SHINHWA_QMS_WORKFLOW/02_REVIEW/구본회수_수령확인_체크시트_20261012.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/02_REVIEW/구본회수_수령확인_체크시트_20261012.xlsx
@@ -539,7 +539,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>참고: 통합문서가 공식 관리본이고, 낱개 단독 문서는 병행(열람·심사 제출용)입니다. SH-WI-001·002 는 통합문서본을 사용합니다.</t>
+          <t>참고: 문서관리대장 수정본15 의 03_배포대장 수령자 칸에는 '조직도 부서 책임자 수령 전제'(사용자 지시 2026-10-12)로 기재되어 있습니다. 실제 수령일·서명은 이 체크시트로 확인해 보완하세요.</t>
         </is>
       </c>
     </row>
